--- a/bankole_sex_specific_splicing_2026/documentation/04_dataPrep_sum_techReps_ujc_erp.xlsx
+++ b/bankole_sex_specific_splicing_2026/documentation/04_dataPrep_sum_techReps_ujc_erp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="117">
   <si>
     <t xml:space="preserve">Dataprep UJC and ERP</t>
   </si>
@@ -84,25 +84,9 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Check that stack files are uniq on jxnHash:
+    <t xml:space="preserve">Check that stack files are uniq on jxnHash:
 PROJ/check_sas_import_ujc_cnt_file_uniq_jxnHash.pdf
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">jxnhash is uniq</t>
-    </r>
+jxnhash is uniq</t>
   </si>
   <si>
     <t xml:space="preserve">Add zeros to ujc counts file 
@@ -143,25 +127,9 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">freqs for checking:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ/expression_output/freqs_onCalls_UJC_counts.pdf
+    <t xml:space="preserve">freqs for checking:
+PROJ/expression_output/freqs_onCalls_UJC_counts.pdf
 PROJ/expression_output/freqs_onCalls_UJC_sexLimited_flag_analyze.pdf</t>
-    </r>
   </si>
   <si>
     <r>
@@ -284,88 +252,13 @@
     <t xml:space="preserve">PROJ/scripts/merge_jxnHas_datafiles_2_5species_full_anno_05amm.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PROJ/Tables/datafile_jxnHash_{species}.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/submission/supplementary/fiveSpecies_{species}_full_annotation.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/erp_and_esp_output/fiveSpecies_2_{species}_ujc_er_vs_{species_data}_data_2_{species}_ujc_noMultiGene_infoERP.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/erp_and_esp_output/fiveSpecies_2_{species}_ujc_es_vs_{species_data}_data_2_{species}_ujc_noMultiGene_infoESP.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">submission/supplementary/datafiles/datafile_jxnHash_{species}_w_ERP_ESP_info.csv</t>
-    </r>
+    <t xml:space="preserve">PROJ/Tables/datafile_jxnHash_{species}.csv
+PROJ/submission/supplementary/fiveSpecies_{species}_full_annotation.csv
+PROJ/erp_and_esp_output/fiveSpecies_2_{species}_ujc_er_vs_{species_data}_data_2_{species}_ujc_noMultiGene_infoERP.csv
+PROJ/erp_and_esp_output/fiveSpecies_2_{species}_ujc_es_vs_{species_data}_data_2_{species}_ujc_noMultiGene_infoESP.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJ/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_ERP_ESP_info.csv</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -384,52 +277,11 @@
     <t xml:space="preserve">PROJ/scripts/add_flag_ERPanno_2_datafile_jxnHash_w_anno.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PROJ/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_ERP_ESP_info.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/submission/supplementary/fiveSpecies_{species}_full_annotation_w_dataFlag.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_ERP_ESP_info_02amm.csv</t>
-    </r>
+    <t xml:space="preserve">PROJ/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_ERP_ESP_info.csv
+PROJ/submission/supplementary/fiveSpecies_{species}_full_annotation_w_dataFlag.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJ/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_ERP_ESP_info_02amm.csv</t>
   </si>
   <si>
     <r>
@@ -493,6 +345,58 @@
     <t xml:space="preserve">{proj}/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_annoFlag_ERP_ESP_info_strCat_flagNovel_02amm.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve errors from duplicate gene names in mel and sim
+    Anno file has 1 geneID and datafile has other 
+create table where the first column contains the mis-assigned geneID and the second column contains the correct geneID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAS/mel_sim_duplicated_geneID_fix.sas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNO/fiveSpecies_2_dmel6_anno_files/dmel650_duplicated_genes.csv
+ANNO/fiveSpecies_2_dsim2_anno_files/dsim202_duplicated_genes.csv $OUTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNO/dmel6_duplicated_geneID_fix.csv
+ANNO/dsim2_duplicated_geneID_fix.csv
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace misassigned geneID in dmel and dsim datafiles with the correct geneID,
+Fix flag_jxnHash_in_full_anno flag,
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCRIPTS/fix_datafile_jxnHash_02amm.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{PROJ}/submission/supplementary_files/datafiles/datafile_jxnHash_dmel6_w_annoFlag_ERP_ESP_info_strCat_flagNovel_02amm.csv
+{PROJ}/zenodo/fiveSpecies_supporting_files/{species}_duplicated_geneID_fix.csv
+{PROJ}/zenodo/fiveSpecies_{species}_full_annotation.csv"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{PROJ}/submission/supplementary_files/datafiles/datafile_jxnHash_{species}_almost.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add genesetID  and componentID 
+     GenesetID on gene
+    ComponentID on jxnHash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCRIPTS/add_geneset_component_2_datafile.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{PROJ}/submission/supplementary_files/datafiles/datafile_jxnHash_{species}_almost.csv
+{proj}/submission/supplementary_files/fiveSpecies_annotations/link_files/component_map_by_node.csv
+{proj}/submission/supplementary_files/fiveSpecies_annotations/link_files/nodes_with_geneset.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{proj}/zenodo/datafiles/datafile_jxnHash_{species}.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">ERP</t>
   </si>
   <si>
@@ -521,7 +425,7 @@
 Import width of ERP = 120</t>
   </si>
   <si>
-    <t xml:space="preserve">PROJ/sas_programs/sum_ERP_techReps.sas</t>
+    <t xml:space="preserve">PROJ/sas_programs/sum_ERP_techReps_02amm.sas</t>
   </si>
   <si>
     <t xml:space="preserve">/TB20/sex_specific_splicing/erp_and_esp_analysis/fiveSpecies_2_&amp;genome._ujc_er_vs_&amp;species._data_2_&amp;genome._ujc_noMultiGene_read_per_ERP.csv</t>
@@ -663,60 +567,11 @@
     <t xml:space="preserve">PROJ/scripts/add_if_ERP_has_putative_novel_jxnHash_2_datafile_erp.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/erp_w_putative_novel_transcript_list.csv
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/submission/supplementary/datafiles/datafile_erp_{species}_w_annoFlag.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/submission/supplementary/datafiles/datafile_erp_{species}_w_annoFlag_flagNovel.csv</t>
-    </r>
+    <t xml:space="preserve">PROJ/erp_w_putative_novel_transcript_list.csv
+PROJ/submission/supplementary/datafiles/datafile_erp_{species}_w_annoFlag.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJ/submission/supplementary/datafiles/datafile_erp_{species}_w_annoFlag_flagNovel.csv</t>
   </si>
   <si>
     <t xml:space="preserve">add sexClass where flag_annotation = 1  ==&gt; sexClass_in_anno
@@ -735,42 +590,7 @@
     <t xml:space="preserve">PROJ/scripts/sexBias_sig_erp_gene_cnts_mel_sim_ser.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">submission/supplementary/datafiles/datafile_erp_{species}_w_annoFlag_flagNovel.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Tables/geneCnts_num_sig_erp_by_Anno_{species}.csv</t>
-    </r>
+    <t xml:space="preserve">PROJ/Tables/geneCnts_num_sig_erp_by_Anno_{species}.csv</t>
   </si>
   <si>
     <t xml:space="preserve">for yak and san sexBias</t>
@@ -779,23 +599,7 @@
     <t xml:space="preserve">PROJ/scripts/sexBias_erp_gene_cnts_yak_san.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PROJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Tables/geneCnts_num_bias_erp_by_Anno_{species}.csv</t>
-    </r>
+    <t xml:space="preserve">PROJ/Tables/geneCnts_num_bias_erp_by_Anno_{species}.csv</t>
   </si>
 </sst>
 </file>
@@ -805,11 +609,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -831,6 +636,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -838,6 +644,7 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -845,18 +652,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -909,12 +704,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -930,32 +729,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1141,90 +928,90 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="67.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="35.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="67.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="36.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="39.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+    <row r="10" s="3" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5" t="s">
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -1234,46 +1021,46 @@
     </row>
     <row r="15" s="7" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6"/>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="6"/>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
     <row r="16" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="6"/>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="J17" s="6"/>
@@ -1282,66 +1069,66 @@
     <row r="19" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="6"/>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
     <row r="20" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>34</v>
       </c>
       <c r="F21" s="8"/>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
     </row>
     <row r="22" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="415.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="6"/>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="6"/>
@@ -1349,23 +1136,23 @@
     </row>
     <row r="25" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>42</v>
       </c>
       <c r="F25" s="6"/>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J25" s="6"/>
@@ -1373,17 +1160,17 @@
     <row r="27" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="6"/>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H27" s="6" t="s">
@@ -1395,20 +1182,20 @@
     <row r="29" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>51</v>
       </c>
       <c r="F29" s="6"/>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I29" s="6"/>
@@ -1417,20 +1204,20 @@
     <row r="31" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8"/>
       <c r="B31" s="6"/>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F31" s="6"/>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I31" s="6"/>
@@ -1448,326 +1235,361 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F33" s="6"/>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="37" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5" t="s">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="8" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E35" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="5" t="s">
+      <c r="G35" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H35" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" s="5" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E37" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="5" t="s">
+      <c r="G37" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H37" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="5" t="s">
+    </row>
+    <row r="39" s="7" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E39" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="G39" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
-      <c r="C43" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>75</v>
       </c>
+      <c r="D43" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="45" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>77</v>
+      <c r="C45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F45" s="6"/>
-      <c r="G45" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>79</v>
+      <c r="G45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="47" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>81</v>
+      <c r="C47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="F47" s="6"/>
-      <c r="G47" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H47" s="5" t="s">
+      <c r="G47" s="6" t="s">
         <v>83</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="49" customFormat="false" ht="303.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H49" s="5" t="s">
+    <row r="49" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-    </row>
-    <row r="51" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
-      <c r="C51" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E51" s="5" t="s">
+      <c r="C51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>89</v>
       </c>
+      <c r="E51" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="F51" s="6"/>
-      <c r="G51" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H51" s="5" t="s">
+      <c r="G51" s="6" t="s">
         <v>91</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="53" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8"/>
+    <row r="53" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6"/>
       <c r="B53" s="6"/>
-      <c r="C53" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E53" s="5" t="s">
+      <c r="C53" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>93</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-    </row>
-    <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="7" customFormat="true" ht="303.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
-      <c r="C55" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" s="5" t="s">
+      <c r="C55" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>97</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-    </row>
-    <row r="57" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>99</v>
+      <c r="C57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-    </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6"/>
+    <row r="59" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8"/>
       <c r="B59" s="6"/>
-      <c r="C59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>103</v>
+      <c r="C59" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="61" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="1"/>
+    </row>
+    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
+      <c r="C61" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="G61" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="1"/>
+    </row>
+    <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+    </row>
+    <row r="67" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
